--- a/수주대장조회.xlsx
+++ b/수주대장조회.xlsx
@@ -60490,7 +60490,7 @@
         <v>85.00</v>
       </c>
       <c r="V343" s="14" t="n">
-        <v>54.00</v>
+        <v>100.00</v>
       </c>
       <c r="W343" s="15" t="n">
         <v>950428.00</v>
@@ -60505,7 +60505,7 @@
         <v>1584</v>
       </c>
       <c r="AA343" s="15" t="n">
-        <v>4035280.68</v>
+        <v>7472742.00</v>
       </c>
       <c r="AB343" s="9" t="s">
         <v>1584</v>
@@ -60580,7 +60580,7 @@
         <v>13503</v>
       </c>
       <c r="AZ343" s="7">
-        <v>46185</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="344" spans="1:52" ht="16.5" customHeight="1">
@@ -85612,7 +85612,7 @@
         <v>81.00</v>
       </c>
       <c r="V502" s="14" t="n">
-        <v>40.00</v>
+        <v>44.00</v>
       </c>
       <c r="W502" s="15" t="n">
         <v>5252719.00</v>
@@ -85627,7 +85627,7 @@
         <v>1584</v>
       </c>
       <c r="AA502" s="15" t="n">
-        <v>15742398.24</v>
+        <v>17316638.07</v>
       </c>
       <c r="AB502" s="9" t="s">
         <v>1584</v>
@@ -85702,7 +85702,7 @@
         <v>13503</v>
       </c>
       <c r="AZ502" s="7">
-        <v>46183</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="503" spans="1:52" ht="16.5" customHeight="1">
@@ -89336,7 +89336,7 @@
         <v>13503</v>
       </c>
       <c r="AZ525" s="7">
-        <v>46184</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="526" spans="1:52" ht="16.5" customHeight="1">
